--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136452523</v>
       </c>
       <c r="B3" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32940-2026 artfynd.xlsx
+++ b/artfynd/A 32940-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136452521</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136452522</v>
       </c>
       <c r="B4" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
